--- a/output/京都第二赤十字病院_随意契約_X線関連.xlsx
+++ b/output/京都第二赤十字病院_随意契約_X線関連.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -670,7 +670,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>透視撮影台（X線テレビ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -685,33 +685,33 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>公表された随意契約に該当なし</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>回診用X線装置</t>
+          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
